--- a/data/trans_bre/P38C-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Provincia-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 13,75</t>
+          <t>-2,79; 13,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,86</t>
+          <t>-1,09; 4,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 20,84</t>
+          <t>-3,66; 19,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,15</t>
+          <t>-1,1; 4,87</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,27</t>
+          <t>2,93; 10,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,24</t>
+          <t>4,22; 17,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,13</t>
+          <t>3,19; 12,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 25,21</t>
+          <t>5,44; 25,41</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,5</t>
+          <t>-1,34; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,1</t>
+          <t>0,41; 8,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,66</t>
+          <t>-1,44; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,11</t>
+          <t>0,48; 9,04</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,14</t>
+          <t>-4,92; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 8,51</t>
+          <t>-38,5; 8,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,45</t>
+          <t>-5,24; 3,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 10,16</t>
+          <t>-42,95; 10,26</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,68</t>
+          <t>4,39; 18,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 13,89</t>
+          <t>-0,29; 14,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 25,94</t>
+          <t>5,44; 25,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 18,25</t>
+          <t>-0,61; 18,48</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 13,21</t>
+          <t>0,75; 13,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,44</t>
+          <t>-1,15; 5,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 17,28</t>
+          <t>0,86; 16,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,08</t>
+          <t>-1,21; 6,05</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,94</t>
+          <t>3,81; 14,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 18,8</t>
+          <t>6,87; 18,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 24,34</t>
+          <t>5,76; 23,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 24,83</t>
+          <t>8,06; 24,52</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,15</t>
+          <t>2,48; 7,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 48,71</t>
+          <t>6,98; 50,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,49</t>
+          <t>2,75; 9,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 237,97</t>
+          <t>11,15; 251,79</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,79</t>
+          <t>4,23; 7,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 28,75</t>
+          <t>4,53; 30,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,64</t>
+          <t>5,08; 9,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 51,8</t>
+          <t>5,62; 52,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38C-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 13,01</t>
+          <t>-2,68; 13,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,57</t>
+          <t>-0,79; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 19,4</t>
+          <t>-3,37; 20,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,87</t>
+          <t>-0,8; 3,83</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,45</t>
+          <t>3,13; 10,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 17,37</t>
+          <t>2,2; 14,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,17</t>
+          <t>3,54; 11,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 25,41</t>
+          <t>2,75; 20,69</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,5</t>
+          <t>-1,67; 7,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,04</t>
+          <t>0,28; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 8,71</t>
+          <t>-1,79; 8,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 9,04</t>
+          <t>0,31; 8,22</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-7,35</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,54%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,21</t>
+          <t>-4,72; 2,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 8,73</t>
+          <t>1,2; 14,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,58</t>
+          <t>-5,0; 3,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 10,26</t>
+          <t>1,34; 18,88</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 18,08</t>
+          <t>4,79; 18,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 14,38</t>
+          <t>1,79; 15,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 25,2</t>
+          <t>6,08; 25,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 18,48</t>
+          <t>2,25; 21,47</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>3,7</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 13,01</t>
+          <t>0,41; 13,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,66</t>
+          <t>-0,04; 7,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 16,67</t>
+          <t>0,46; 17,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,05</t>
+          <t>0,03; 8,57</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 14,23</t>
+          <t>4,05; 14,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 18,76</t>
+          <t>4,02; 12,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 23,29</t>
+          <t>6,11; 23,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,52</t>
+          <t>4,69; 16,14</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,97</t>
+          <t>2,5; 8,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 50,04</t>
+          <t>4,71; 14,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,17</t>
+          <t>2,74; 9,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 251,79</t>
+          <t>7,6; 25,47</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,57</t>
+          <t>4,13; 7,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 30,02</t>
+          <t>5,14; 9,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,42</t>
+          <t>4,96; 9,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 52,69</t>
+          <t>6,35; 12,02</t>
         </is>
       </c>
     </row>
